--- a/scripts/fixtures/opt-test-crm.xlsx
+++ b/scripts/fixtures/opt-test-crm.xlsx
@@ -2,41 +2,228 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Заявка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="162913" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="20">
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <charset val="204"/>
+      <family val="2"/>
       <sz val="11"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="8"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="10"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color indexed="10"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Verdana"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Nunito"/>
+      <color rgb="FF323232"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.5999938962981048"/>
+        <bgColor rgb="FFF4F3E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.3999755851924192"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -44,18 +231,437 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="-0.249946592608417"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </right>
+      <top style="thick">
+        <color theme="5" tint="0.3999450666829432"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6" tint="0.3999450666829432"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="16" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="12" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -128,9 +734,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -138,44 +744,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -202,14 +808,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -236,9 +843,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -247,160 +855,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -413,149 +992,594 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Y14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col width="14.42578125" customWidth="1" style="6" min="1" max="1"/>
+    <col width="49" customWidth="1" style="6" min="2" max="3"/>
+    <col width="18.85546875" customWidth="1" style="6" min="4" max="4"/>
+    <col width="27" customWidth="1" style="6" min="5" max="5"/>
+    <col width="17.28515625" customWidth="1" style="45" min="6" max="6"/>
+    <col width="14.42578125" customWidth="1" style="45" min="7" max="9"/>
+  </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6">
+      <c r="B1" s="23" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="43" t="n"/>
+      <c r="G1" s="43" t="n"/>
+      <c r="H1" s="43" t="n"/>
+      <c r="I1" s="43" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" s="6">
+      <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>Ставка</t>
+          <t>Заявка</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Ставка НДС:</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
+      <c r="F2" s="44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G2" s="44" t="n"/>
+      <c r="H2" s="44" t="n"/>
+      <c r="I2" s="44" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+    <row r="3" ht="86.25" customHeight="1" s="6">
+      <c r="A3" s="12" t="n"/>
+      <c r="B3" s="29" t="inlineStr">
         <is>
-          <t>ИНН Поставщик-продавец
-(лавка поставщик)</t>
+          <t>ИНН Компании-продавца
+(Наши компании)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
-          <t>ИНН Покупатель-плательщик
-(лавка покупатель)</t>
+          <t>ИНН Компании-покупатели
+(Ваши компании)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>Дата с/ф
-(дата док. счета)</t>
+(дд. мм. гггг)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="36" t="inlineStr">
         <is>
-          <t>Сумма платежа
-(руб с НДС сверху)</t>
+          <t>Сумма покупок
+(НДС в том числе)</t>
         </is>
       </c>
+      <c r="F3" s="44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G3" s="44" t="inlineStr">
+        <is>
+          <t>БН</t>
+        </is>
+      </c>
+      <c r="H3" s="44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I3" s="55" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
+      <c r="Y3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+    <row r="4" ht="15.75" customHeight="1" s="6">
+      <c r="A4" s="12" t="n"/>
+      <c r="B4" s="35" t="n">
+        <v>7703822568</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>5507266215</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <v>45679</v>
+      </c>
+      <c r="E4" s="37" t="n">
+        <v>314752</v>
+      </c>
+      <c r="F4" s="56">
+        <f>E4/100*F3</f>
+        <v/>
+      </c>
+      <c r="G4" s="43" t="n"/>
+      <c r="H4" s="43" t="n"/>
+      <c r="I4" s="43" t="n"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="6">
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="35" t="n">
+        <v>7703822568</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>5507266215</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <v>45700</v>
+      </c>
+      <c r="E5" s="37" t="n">
+        <v>342500</v>
+      </c>
+      <c r="F5" s="56">
+        <f>E5/100*F3</f>
+        <v/>
+      </c>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
+      <c r="I5" s="43" t="n"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" s="6">
+      <c r="A6" s="12" t="n"/>
+      <c r="B6" s="35" t="n">
+        <v>7713151911</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>5507266215</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>45712</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>311207</v>
+      </c>
+      <c r="F6" s="56">
+        <f>E6/100*F3</f>
+        <v/>
+      </c>
+      <c r="G6" s="43" t="n"/>
+      <c r="H6" s="43" t="n"/>
+      <c r="I6" s="43" t="n"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" s="6">
+      <c r="A7" s="12" t="n"/>
+      <c r="B7" s="35" t="n">
+        <v>7713151911</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>5507266215</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <v>45726</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>265300</v>
+      </c>
+      <c r="F7" s="56">
+        <f>E7/100*F3</f>
+        <v/>
+      </c>
+      <c r="G7" s="43" t="n"/>
+      <c r="H7" s="43" t="n"/>
+      <c r="I7" s="43" t="n"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" s="6">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="35" t="n">
+        <v>7720313708</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>5507266215</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>45735</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>395671</v>
+      </c>
+      <c r="F8" s="56">
+        <f>E8/100*F3</f>
+        <v/>
+      </c>
+      <c r="G8" s="43" t="n"/>
+      <c r="H8" s="43" t="n"/>
+      <c r="I8" s="43" t="n"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="6">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="56" t="n"/>
+      <c r="G9" s="43" t="n"/>
+      <c r="H9" s="43" t="n"/>
+      <c r="I9" s="43" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="6">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="31" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="56" t="n"/>
+      <c r="G10" s="43" t="n"/>
+      <c r="H10" s="43" t="n"/>
+      <c r="I10" s="43" t="n"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" s="6">
+      <c r="A11" s="12" t="n"/>
+      <c r="B11" s="35" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="56" t="n"/>
+      <c r="G11" s="43" t="n"/>
+      <c r="H11" s="43" t="n"/>
+      <c r="I11" s="43" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="6">
+      <c r="A12" s="12" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="43" t="n"/>
+      <c r="H12" s="43" t="n"/>
+      <c r="I12" s="43" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" s="6">
+      <c r="A13" s="12" t="n"/>
+      <c r="B13" s="33" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="32" t="n"/>
+      <c r="E13" s="37">
+        <f>SUM(E4:E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="57">
+        <f>SUM(F4:F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="58">
+        <f>F13*1.19</f>
+        <v/>
+      </c>
+      <c r="H13" s="56">
+        <f>E13/100*H3</f>
+        <v/>
+      </c>
+      <c r="I13" s="57">
+        <f>E13*I3/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="6">
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="32" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="43" t="inlineStr">
         <is>
-          <t>7703822568</t>
+          <t>бн</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="G14" s="43" t="inlineStr">
         <is>
-          <t>5507266215</t>
+          <t>нал</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>45679</v>
-      </c>
-      <c r="E4" t="n">
-        <v>314752</v>
+      <c r="H14" s="43" t="n"/>
+      <c r="I14" s="56">
+        <f>I13-G13</f>
+        <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7743622734</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5507266215</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45685</v>
-      </c>
-      <c r="E5" t="n">
-        <v>186420</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7713151911</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5507266215</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>45693</v>
-      </c>
-      <c r="E6" t="n">
-        <v>92500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7720313708</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5507266215</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45700</v>
-      </c>
-      <c r="E7" t="n">
-        <v>203150</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7730303346</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5507266215</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45708</v>
-      </c>
-      <c r="E8" t="n">
-        <v>150000</v>
-      </c>
-    </row>
+    <row r="15" ht="15.75" customHeight="1" s="6"/>
+    <row r="16" ht="15.75" customHeight="1" s="6"/>
+    <row r="17" ht="15.75" customHeight="1" s="6"/>
+    <row r="18" ht="15.75" customHeight="1" s="6"/>
+    <row r="19" ht="15.75" customHeight="1" s="6"/>
+    <row r="20" ht="15.75" customHeight="1" s="6"/>
+    <row r="21" ht="15.75" customHeight="1" s="6"/>
+    <row r="22" ht="15.75" customHeight="1" s="6"/>
+    <row r="23" ht="15.75" customHeight="1" s="6"/>
+    <row r="24" ht="15.75" customHeight="1" s="6"/>
+    <row r="25" ht="15.75" customHeight="1" s="6"/>
+    <row r="26" ht="15.75" customHeight="1" s="6"/>
+    <row r="27" ht="15.75" customHeight="1" s="6"/>
+    <row r="28" ht="15.75" customHeight="1" s="6"/>
+    <row r="29" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="30" ht="15.75" customHeight="1" s="6" thickTop="1"/>
+    <row r="31" ht="15.75" customHeight="1" s="6"/>
+    <row r="32" ht="45" customHeight="1" s="6"/>
+    <row r="33" ht="15.75" customHeight="1" s="6"/>
+    <row r="34" ht="15.75" customHeight="1" s="6"/>
+    <row r="35" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="36" ht="15.75" customHeight="1" s="6" thickTop="1"/>
+    <row r="37" ht="15.75" customHeight="1" s="6"/>
+    <row r="38" ht="15.75" customHeight="1" s="6"/>
+    <row r="39" ht="15.75" customHeight="1" s="6"/>
+    <row r="40" ht="15.75" customHeight="1" s="6"/>
+    <row r="41" ht="15.75" customHeight="1" s="6"/>
+    <row r="42" ht="15.75" customHeight="1" s="6"/>
+    <row r="43" ht="15.75" customHeight="1" s="6"/>
+    <row r="44" ht="15.75" customHeight="1" s="6"/>
+    <row r="45" ht="15.75" customHeight="1" s="6"/>
+    <row r="46" ht="15.75" customHeight="1" s="6"/>
+    <row r="47" ht="15.75" customHeight="1" s="6"/>
+    <row r="48" ht="15.75" customHeight="1" s="6"/>
+    <row r="49" ht="15.75" customHeight="1" s="6"/>
+    <row r="50" ht="15.75" customHeight="1" s="6"/>
+    <row r="51" ht="15.75" customHeight="1" s="6"/>
+    <row r="52" ht="15.75" customHeight="1" s="6"/>
+    <row r="53" ht="15.75" customHeight="1" s="6"/>
+    <row r="54" ht="15.75" customHeight="1" s="6"/>
+    <row r="55" ht="15.75" customHeight="1" s="6"/>
+    <row r="56" ht="15.75" customHeight="1" s="6"/>
+    <row r="57" ht="15.75" customHeight="1" s="6"/>
+    <row r="58" ht="15.75" customHeight="1" s="6"/>
+    <row r="59" ht="15.75" customHeight="1" s="6"/>
+    <row r="60" ht="15.75" customHeight="1" s="6"/>
+    <row r="61" ht="15.75" customHeight="1" s="6"/>
+    <row r="62" ht="15.75" customHeight="1" s="6"/>
+    <row r="63" ht="15.75" customHeight="1" s="6"/>
+    <row r="64" ht="15.75" customHeight="1" s="6"/>
+    <row r="65" ht="15.75" customHeight="1" s="6"/>
+    <row r="66" ht="15.75" customHeight="1" s="6"/>
+    <row r="67" ht="15.75" customHeight="1" s="6"/>
+    <row r="68" ht="15.75" customHeight="1" s="6"/>
+    <row r="69" ht="15.75" customHeight="1" s="6"/>
+    <row r="70" ht="15.75" customHeight="1" s="6"/>
+    <row r="71" ht="15.75" customHeight="1" s="6"/>
+    <row r="72" ht="15.75" customHeight="1" s="6"/>
+    <row r="73" ht="15.75" customHeight="1" s="6"/>
+    <row r="74" ht="15.75" customHeight="1" s="6"/>
+    <row r="75" ht="15.75" customHeight="1" s="6"/>
+    <row r="76" ht="15.75" customHeight="1" s="6"/>
+    <row r="77" ht="15.75" customHeight="1" s="6"/>
+    <row r="78" ht="15.75" customHeight="1" s="6"/>
+    <row r="79" ht="15.75" customHeight="1" s="6"/>
+    <row r="80" ht="15.75" customHeight="1" s="6"/>
+    <row r="81" ht="15.75" customHeight="1" s="6"/>
+    <row r="82" ht="15.75" customHeight="1" s="6"/>
+    <row r="83" ht="15.75" customHeight="1" s="6"/>
+    <row r="84" ht="15.75" customHeight="1" s="6"/>
+    <row r="85" ht="15.75" customHeight="1" s="6"/>
+    <row r="86" ht="15.75" customHeight="1" s="6"/>
+    <row r="87" ht="15.75" customHeight="1" s="6"/>
+    <row r="88" ht="15.75" customHeight="1" s="6"/>
+    <row r="89" ht="15.75" customHeight="1" s="6"/>
+    <row r="90" ht="15.75" customHeight="1" s="6"/>
+    <row r="91" ht="15.75" customHeight="1" s="6"/>
+    <row r="92" ht="15.75" customHeight="1" s="6"/>
+    <row r="93" ht="15.75" customHeight="1" s="6"/>
+    <row r="94" ht="15.75" customHeight="1" s="6"/>
+    <row r="95" ht="15.75" customHeight="1" s="6"/>
+    <row r="96" ht="15.75" customHeight="1" s="6"/>
+    <row r="97" ht="15.75" customHeight="1" s="6"/>
+    <row r="98" ht="15.75" customHeight="1" s="6"/>
+    <row r="99" ht="15.75" customHeight="1" s="6"/>
+    <row r="100" ht="15.75" customHeight="1" s="6"/>
+    <row r="101" ht="15.75" customHeight="1" s="6"/>
+    <row r="102" ht="15.75" customHeight="1" s="6"/>
+    <row r="103" ht="15.75" customHeight="1" s="6"/>
+    <row r="104" ht="15.75" customHeight="1" s="6"/>
+    <row r="105" ht="15.75" customHeight="1" s="6"/>
+    <row r="106" ht="15.75" customHeight="1" s="6"/>
+    <row r="107" ht="15.75" customHeight="1" s="6"/>
+    <row r="108" ht="15.75" customHeight="1" s="6"/>
+    <row r="109" ht="15.75" customHeight="1" s="6"/>
+    <row r="110" ht="15.75" customHeight="1" s="6"/>
+    <row r="111" ht="15.75" customHeight="1" s="6"/>
+    <row r="112" ht="15.75" customHeight="1" s="6"/>
+    <row r="113" ht="15.75" customHeight="1" s="6"/>
+    <row r="114" ht="15.75" customHeight="1" s="6"/>
+    <row r="115" ht="15.75" customHeight="1" s="6"/>
+    <row r="116" ht="15.75" customHeight="1" s="6"/>
+    <row r="117" ht="15.75" customHeight="1" s="6"/>
+    <row r="118" ht="15.75" customHeight="1" s="6"/>
+    <row r="119" ht="15.75" customHeight="1" s="6"/>
+    <row r="120" ht="15.75" customHeight="1" s="6"/>
+    <row r="121" ht="15.75" customHeight="1" s="6"/>
+    <row r="122" ht="15.75" customHeight="1" s="6"/>
+    <row r="123" ht="15.75" customHeight="1" s="6"/>
+    <row r="124" ht="15.75" customHeight="1" s="6"/>
+    <row r="125" ht="15.75" customHeight="1" s="6"/>
+    <row r="126" ht="15.75" customHeight="1" s="6"/>
+    <row r="127" ht="15.75" customHeight="1" s="6"/>
+    <row r="128" ht="15.75" customHeight="1" s="6"/>
+    <row r="129" ht="15.75" customHeight="1" s="6"/>
+    <row r="130" ht="15.75" customHeight="1" s="6"/>
+    <row r="131" ht="15.75" customHeight="1" s="6"/>
+    <row r="132" ht="15.75" customHeight="1" s="6"/>
+    <row r="133" ht="15.75" customHeight="1" s="6"/>
+    <row r="134" ht="15.75" customHeight="1" s="6"/>
+    <row r="135" ht="15.75" customHeight="1" s="6"/>
+    <row r="136" ht="15.75" customHeight="1" s="6"/>
+    <row r="137" ht="15.75" customHeight="1" s="6"/>
+    <row r="138" ht="15.75" customHeight="1" s="6"/>
+    <row r="139" ht="15.75" customHeight="1" s="6"/>
+    <row r="140" ht="15.75" customHeight="1" s="6"/>
+    <row r="141" ht="15.75" customHeight="1" s="6"/>
+    <row r="142" ht="15.75" customHeight="1" s="6"/>
+    <row r="143" ht="15.75" customHeight="1" s="6"/>
+    <row r="144" ht="15.75" customHeight="1" s="6"/>
+    <row r="145" ht="15.75" customHeight="1" s="6"/>
+    <row r="146" ht="15.75" customHeight="1" s="6"/>
+    <row r="147" ht="15.75" customHeight="1" s="6"/>
+    <row r="148" ht="15.75" customHeight="1" s="6"/>
+    <row r="149" ht="15.75" customHeight="1" s="6"/>
+    <row r="150" ht="15.75" customHeight="1" s="6"/>
+    <row r="151" ht="15.75" customHeight="1" s="6"/>
+    <row r="152" ht="15.75" customHeight="1" s="6"/>
+    <row r="153" ht="15.75" customHeight="1" s="6"/>
+    <row r="154" ht="15.75" customHeight="1" s="6"/>
+    <row r="155" ht="15.75" customHeight="1" s="6"/>
+    <row r="156" ht="15.75" customHeight="1" s="6"/>
+    <row r="157" ht="15.75" customHeight="1" s="6"/>
+    <row r="158" ht="15.75" customHeight="1" s="6"/>
+    <row r="159" ht="15.75" customHeight="1" s="6"/>
+    <row r="160" ht="15.75" customHeight="1" s="6"/>
+    <row r="161" ht="15.75" customHeight="1" s="6"/>
+    <row r="162" ht="15.75" customHeight="1" s="6"/>
+    <row r="163" ht="15.75" customHeight="1" s="6"/>
+    <row r="164" ht="15.75" customHeight="1" s="6"/>
+    <row r="165" ht="15.75" customHeight="1" s="6"/>
+    <row r="166" ht="15.75" customHeight="1" s="6"/>
+    <row r="167" ht="15.75" customHeight="1" s="6"/>
+    <row r="168" ht="15.75" customHeight="1" s="6"/>
+    <row r="169" ht="15.75" customHeight="1" s="6"/>
+    <row r="170" ht="15.75" customHeight="1" s="6"/>
+    <row r="171" ht="15.75" customHeight="1" s="6"/>
+    <row r="172" ht="15.75" customHeight="1" s="6"/>
+    <row r="173" ht="15.75" customHeight="1" s="6"/>
+    <row r="174" ht="15.75" customHeight="1" s="6"/>
+    <row r="175" ht="15.75" customHeight="1" s="6"/>
+    <row r="176" ht="15.75" customHeight="1" s="6"/>
+    <row r="177" ht="15.75" customHeight="1" s="6"/>
+    <row r="178" ht="15.75" customHeight="1" s="6"/>
+    <row r="179" ht="15.75" customHeight="1" s="6"/>
+    <row r="180" ht="15.75" customHeight="1" s="6"/>
+    <row r="181" ht="15.75" customHeight="1" s="6"/>
+    <row r="182" ht="15.75" customHeight="1" s="6"/>
+    <row r="183" ht="15.75" customHeight="1" s="6"/>
+    <row r="184" ht="15.75" customHeight="1" s="6"/>
+    <row r="185" ht="15.75" customHeight="1" s="6"/>
+    <row r="186" ht="15.75" customHeight="1" s="6"/>
+    <row r="187" ht="15.75" customHeight="1" s="6"/>
+    <row r="188" ht="15.75" customHeight="1" s="6"/>
+    <row r="189" ht="15.75" customHeight="1" s="6"/>
+    <row r="190" ht="15.75" customHeight="1" s="6"/>
+    <row r="191" ht="15.75" customHeight="1" s="6"/>
+    <row r="192" ht="15.75" customHeight="1" s="6"/>
+    <row r="193" ht="15.75" customHeight="1" s="6"/>
+    <row r="194" ht="15.75" customHeight="1" s="6"/>
+    <row r="195" ht="15.75" customHeight="1" s="6"/>
+    <row r="196" ht="15.75" customHeight="1" s="6"/>
+    <row r="197" ht="15.75" customHeight="1" s="6"/>
+    <row r="198" ht="15.75" customHeight="1" s="6"/>
+    <row r="199" ht="15.75" customHeight="1" s="6"/>
+    <row r="200" ht="15.75" customHeight="1" s="6"/>
+    <row r="201" ht="15.75" customHeight="1" s="6"/>
+    <row r="202" ht="15.75" customHeight="1" s="6"/>
+    <row r="203" ht="15.75" customHeight="1" s="6"/>
+    <row r="204" ht="15.75" customHeight="1" s="6"/>
+    <row r="205" ht="15.75" customHeight="1" s="6"/>
+    <row r="206" ht="15.75" customHeight="1" s="6"/>
+    <row r="207" ht="15.75" customHeight="1" s="6"/>
+    <row r="208" ht="15.75" customHeight="1" s="6"/>
+    <row r="209" ht="15.75" customHeight="1" s="6"/>
+    <row r="210" ht="15.75" customHeight="1" s="6"/>
+    <row r="211" ht="15.75" customHeight="1" s="6"/>
+    <row r="212" ht="15.75" customHeight="1" s="6"/>
+    <row r="213" ht="15.75" customHeight="1" s="6"/>
+    <row r="214" ht="15.75" customHeight="1" s="6"/>
+    <row r="215" ht="15.75" customHeight="1" s="6"/>
+    <row r="216" ht="15.75" customHeight="1" s="6"/>
+    <row r="217" ht="15.75" customHeight="1" s="6"/>
+    <row r="218" ht="15.75" customHeight="1" s="6"/>
+    <row r="219" ht="15.75" customHeight="1" s="6"/>
+    <row r="220" ht="15.75" customHeight="1" s="6"/>
+    <row r="221" ht="15.75" customHeight="1" s="6"/>
+    <row r="222" ht="15.75" customHeight="1" s="6"/>
+    <row r="223" ht="15.75" customHeight="1" s="6"/>
+    <row r="224" ht="15.75" customHeight="1" s="6"/>
+    <row r="225" ht="15.75" customHeight="1" s="6"/>
+    <row r="226" ht="15.75" customHeight="1" s="6"/>
+    <row r="227" ht="15.75" customHeight="1" s="6"/>
+    <row r="228" ht="15.75" customHeight="1" s="6"/>
+    <row r="229" ht="15.75" customHeight="1" s="6"/>
+    <row r="230" ht="15.75" customHeight="1" s="6"/>
+    <row r="231" ht="15.75" customHeight="1" s="6"/>
+    <row r="232" ht="15.75" customHeight="1" s="6"/>
+    <row r="233" ht="15.75" customHeight="1" s="6"/>
+    <row r="234" ht="15.75" customHeight="1" s="6"/>
+    <row r="235" ht="15.75" customHeight="1" s="6"/>
+    <row r="236" ht="15.75" customHeight="1" s="6"/>
+    <row r="237" ht="15.75" customHeight="1" s="6"/>
+    <row r="238" ht="15.75" customHeight="1" s="6"/>
+    <row r="239" ht="15.75" customHeight="1" s="6"/>
+    <row r="240" ht="15.75" customHeight="1" s="6"/>
+    <row r="241" ht="15.75" customHeight="1" s="6"/>
+    <row r="242" ht="15.75" customHeight="1" s="6"/>
+    <row r="243" ht="15.75" customHeight="1" s="6"/>
+    <row r="244" ht="15.75" customHeight="1" s="6"/>
+    <row r="245" ht="15.75" customHeight="1" s="6"/>
+    <row r="246" ht="15.75" customHeight="1" s="6"/>
+    <row r="247" ht="15.75" customHeight="1" s="6"/>
+    <row r="248" ht="15.75" customHeight="1" s="6"/>
+    <row r="249" ht="15.75" customHeight="1" s="6"/>
+    <row r="250" ht="15.75" customHeight="1" s="6"/>
+    <row r="251" ht="15.75" customHeight="1" s="6"/>
+    <row r="252" ht="15.75" customHeight="1" s="6"/>
+    <row r="253" ht="15.75" customHeight="1" s="6"/>
+    <row r="254" ht="15.75" customHeight="1" s="6"/>
+    <row r="255" ht="15.75" customHeight="1" s="6"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="3">
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B30:E30"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="D2 D31" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"10,20"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B13:B17 B20:B23 B27:B30 B36:B255" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Введите корректный ИНН" type="custom">
+      <formula1>is_valid_inn(B11)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B25:B26 B33:B34 C33" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Введите корректный ИНН" type="custom">
+      <formula1>is_valid_inn(#REF!)</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18:B19" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Введите корректный ИНН" type="custom">
+      <formula1>is_valid_inn(B4)</formula1>
+    </dataValidation>
+    <dataValidation sqref="D4:D23 D33:D34" showDropDown="1" showInputMessage="1" showErrorMessage="1" allowBlank="1" prompt="Enter a valid date"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>